--- a/data/freight/HARPEX.xlsx
+++ b/data/freight/HARPEX.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A623355A-F93D-4DE5-BC02-11EB6FC3E22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040A51DE-EB3E-43F9-9E93-114D7FC299A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF65146B-3FFB-48AE-A8B4-72212067DCD1}"/>
   </bookViews>
   <sheets>
     <sheet name="HARPEX" sheetId="1" r:id="rId1"/>
-    <sheet name="info" sheetId="2" r:id="rId2"/>
+    <sheet name="fig" sheetId="3" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -103,7 +104,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +121,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -141,11 +149,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -173,10 +182,25 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -189,6 +213,1014 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>HARPEX!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> HARPEX </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>HARPEX!$B$2:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>46017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46024</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46031</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46038</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46073</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46115</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46122</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46129</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46136</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46150</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46157</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46164</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46171</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>HARPEX!$E$2:$E$24</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>2180.56</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2182</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2182</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2182</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2184</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2184</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2184</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2191</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2206</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2213</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2213</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2213</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2213</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2213</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2213</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2240</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2256</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2256</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2263</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2292</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2318</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2321</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2322.3000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1114-440C-AC9D-FC7CBE807D44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="48987840"/>
+        <c:axId val="48971520"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="48987840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+          <c:min val="46023"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48971520"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="2"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="48971520"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="48987840"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ACCCC30-D39C-4238-B136-03B978188F4E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD65D719-F701-4D19-8EAC-1946AFF5D321}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" style="1" customWidth="1"/>
@@ -546,56 +1578,36 @@
       </c>
       <c r="P1" s="7"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>46024</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46024</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3">
-        <v>2182</v>
-      </c>
-      <c r="F2" s="4">
-        <v>10250</v>
-      </c>
-      <c r="G2" s="4">
-        <v>16500</v>
-      </c>
-      <c r="H2" s="4">
-        <v>27500</v>
-      </c>
-      <c r="I2" s="4">
-        <v>32000</v>
-      </c>
-      <c r="J2" s="4">
-        <v>35500</v>
-      </c>
-      <c r="K2" s="4">
-        <v>37500</v>
-      </c>
-      <c r="L2" s="4">
-        <v>44000</v>
-      </c>
-      <c r="M2" s="4">
-        <v>53000</v>
-      </c>
-      <c r="N2" s="4">
-        <v>66000</v>
-      </c>
-      <c r="O2" s="4">
-        <v>74000</v>
-      </c>
-      <c r="P2" s="2"/>
+    <row r="2" spans="1:16" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>46017</v>
+      </c>
+      <c r="B2" s="12">
+        <v>46017</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="14">
+        <v>2180.56</v>
+      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="13"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>46031</v>
+        <v>46024</v>
       </c>
       <c r="B3" s="1">
-        <v>46031</v>
+        <v>46024</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -636,10 +1648,10 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="B4" s="1">
-        <v>46038</v>
+        <v>46031</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -680,21 +1692,21 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="B5" s="1">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3">
-        <v>2184</v>
+        <v>2182</v>
       </c>
       <c r="F5" s="4">
         <v>10250</v>
       </c>
       <c r="G5" s="4">
-        <v>16750</v>
+        <v>16500</v>
       </c>
       <c r="H5" s="4">
         <v>27500</v>
@@ -724,59 +1736,103 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="B6" s="1">
-        <v>46052</v>
+        <v>46045</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+      <c r="E6" s="3">
+        <v>2184</v>
+      </c>
+      <c r="F6" s="4">
+        <v>10250</v>
+      </c>
+      <c r="G6" s="4">
+        <v>16750</v>
+      </c>
+      <c r="H6" s="4">
+        <v>27500</v>
+      </c>
+      <c r="I6" s="4">
+        <v>32000</v>
+      </c>
+      <c r="J6" s="4">
+        <v>35500</v>
+      </c>
+      <c r="K6" s="4">
+        <v>37500</v>
+      </c>
+      <c r="L6" s="4">
+        <v>44000</v>
+      </c>
+      <c r="M6" s="4">
+        <v>53000</v>
+      </c>
+      <c r="N6" s="4">
+        <v>66000</v>
+      </c>
+      <c r="O6" s="4">
+        <v>74000</v>
+      </c>
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="B7" s="1">
-        <v>46059</v>
+        <v>46052</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+      <c r="E7" s="3">
+        <v>2184</v>
+      </c>
+      <c r="F7" s="4">
+        <v>10250</v>
+      </c>
+      <c r="G7" s="4">
+        <v>16750</v>
+      </c>
+      <c r="H7" s="4">
+        <v>27500</v>
+      </c>
+      <c r="I7" s="4">
+        <v>32000</v>
+      </c>
+      <c r="J7" s="4">
+        <v>35500</v>
+      </c>
+      <c r="K7" s="4">
+        <v>37500</v>
+      </c>
+      <c r="L7" s="4">
+        <v>44000</v>
+      </c>
+      <c r="M7" s="4">
+        <v>53000</v>
+      </c>
+      <c r="N7" s="4">
+        <v>66000</v>
+      </c>
+      <c r="O7" s="4">
+        <v>74000</v>
+      </c>
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="B8" s="1">
-        <v>46066</v>
+        <v>46059</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="3">
-        <v>2191</v>
+        <v>2184</v>
       </c>
       <c r="F8" s="4">
         <v>10250</v>
@@ -785,22 +1841,22 @@
         <v>16750</v>
       </c>
       <c r="H8" s="4">
-        <v>28000</v>
+        <v>27500</v>
       </c>
       <c r="I8" s="4">
         <v>32000</v>
       </c>
       <c r="J8" s="4">
-        <v>37000</v>
+        <v>35500</v>
       </c>
       <c r="K8" s="4">
-        <v>39000</v>
+        <v>37500</v>
       </c>
       <c r="L8" s="4">
-        <v>43000</v>
+        <v>44000</v>
       </c>
       <c r="M8" s="4">
-        <v>52000</v>
+        <v>53000</v>
       </c>
       <c r="N8" s="4">
         <v>66000</v>
@@ -812,24 +1868,24 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="B9" s="1">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="3">
-        <v>2206</v>
+        <v>2191</v>
       </c>
       <c r="F9" s="4">
-        <v>10750</v>
+        <v>10250</v>
       </c>
       <c r="G9" s="4">
         <v>16750</v>
       </c>
       <c r="H9" s="4">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="I9" s="4">
         <v>32000</v>
@@ -856,18 +1912,18 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>46080</v>
+        <v>46073</v>
       </c>
       <c r="B10" s="1">
-        <v>46080</v>
+        <v>46073</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="3">
-        <v>2213</v>
+        <v>2206</v>
       </c>
       <c r="F10" s="4">
-        <v>11000</v>
+        <v>10750</v>
       </c>
       <c r="G10" s="4">
         <v>16750</v>
@@ -900,10 +1956,10 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="B11" s="1">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -944,10 +2000,10 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="B12" s="1">
-        <v>46094</v>
+        <v>46087</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -988,10 +2044,10 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>46101</v>
+        <v>46094</v>
       </c>
       <c r="B13" s="1">
-        <v>46101</v>
+        <v>46094</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1032,10 +2088,10 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="B14" s="1">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1076,10 +2132,10 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>46115</v>
+        <v>46108</v>
       </c>
       <c r="B15" s="1">
-        <v>46115</v>
+        <v>46108</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -1120,36 +2176,60 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>46122</v>
+        <v>46115</v>
       </c>
       <c r="B16" s="1">
-        <v>46122</v>
+        <v>46115</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
+      <c r="E16" s="3">
+        <v>2213</v>
+      </c>
+      <c r="F16" s="4">
+        <v>11000</v>
+      </c>
+      <c r="G16" s="4">
+        <v>16750</v>
+      </c>
+      <c r="H16" s="4">
+        <v>25000</v>
+      </c>
+      <c r="I16" s="4">
+        <v>32000</v>
+      </c>
+      <c r="J16" s="4">
+        <v>37000</v>
+      </c>
+      <c r="K16" s="4">
+        <v>39000</v>
+      </c>
+      <c r="L16" s="4">
+        <v>43000</v>
+      </c>
+      <c r="M16" s="4">
+        <v>52000</v>
+      </c>
+      <c r="N16" s="4">
+        <v>66000</v>
+      </c>
+      <c r="O16" s="4">
+        <v>74000</v>
+      </c>
       <c r="P16" s="2"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <v>46129</v>
+        <v>46122</v>
       </c>
       <c r="B17" s="1">
-        <v>46129</v>
+        <v>46122</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
+      <c r="E17" s="3">
+        <v>2240</v>
+      </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -1164,14 +2244,16 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <v>46136</v>
+        <v>46129</v>
       </c>
       <c r="B18" s="1">
-        <v>46136</v>
+        <v>46129</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="E18" s="3">
+        <v>2256</v>
+      </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -1186,54 +2268,37 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="B19" s="1">
-        <v>46143</v>
-      </c>
-      <c r="E19" s="5">
-        <v>2263</v>
-      </c>
-      <c r="F19" s="5">
-        <v>11250</v>
-      </c>
-      <c r="G19" s="5">
-        <v>17250</v>
-      </c>
-      <c r="H19" s="5">
-        <v>28000</v>
-      </c>
-      <c r="I19" s="5">
-        <v>33000</v>
-      </c>
-      <c r="J19" s="5">
-        <v>38000</v>
-      </c>
-      <c r="K19" s="5">
-        <v>40000</v>
-      </c>
-      <c r="L19" s="5">
-        <v>45000</v>
-      </c>
-      <c r="M19" s="5">
-        <v>56000</v>
-      </c>
-      <c r="N19" s="5">
-        <v>67000</v>
-      </c>
-      <c r="O19" s="5">
-        <v>75000</v>
-      </c>
+        <v>46136</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3">
+        <v>2256</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="2"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="B20" s="1">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="E20" s="5">
-        <v>2292</v>
+        <v>2263</v>
       </c>
       <c r="F20" s="5">
         <v>11250</v>
@@ -1254,33 +2319,33 @@
         <v>40000</v>
       </c>
       <c r="L20" s="5">
-        <v>46000</v>
+        <v>45000</v>
       </c>
       <c r="M20" s="5">
-        <v>57000</v>
+        <v>56000</v>
       </c>
       <c r="N20" s="5">
-        <v>69000</v>
+        <v>67000</v>
       </c>
       <c r="O20" s="5">
-        <v>76000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="B21" s="1">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="E21" s="5">
-        <v>2318</v>
+        <v>2292</v>
       </c>
       <c r="F21" s="5">
         <v>11250</v>
       </c>
       <c r="G21" s="5">
-        <v>17500</v>
+        <v>17250</v>
       </c>
       <c r="H21" s="5">
         <v>28000</v>
@@ -1301,21 +2366,21 @@
         <v>57000</v>
       </c>
       <c r="N21" s="5">
-        <v>71000</v>
+        <v>69000</v>
       </c>
       <c r="O21" s="5">
-        <v>78000</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>46164</v>
+        <v>46157</v>
       </c>
       <c r="B22" s="1">
-        <v>46164</v>
+        <v>46157</v>
       </c>
       <c r="E22" s="5">
-        <v>2321</v>
+        <v>2318</v>
       </c>
       <c r="F22" s="5">
         <v>11250</v>
@@ -1324,10 +2389,10 @@
         <v>17500</v>
       </c>
       <c r="H22" s="5">
-        <v>28500</v>
+        <v>28000</v>
       </c>
       <c r="I22" s="5">
-        <v>33500</v>
+        <v>33000</v>
       </c>
       <c r="J22" s="5">
         <v>38000</v>
@@ -1345,6 +2410,88 @@
         <v>71000</v>
       </c>
       <c r="O22" s="5">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46164</v>
+      </c>
+      <c r="E23" s="5">
+        <v>2321</v>
+      </c>
+      <c r="F23" s="5">
+        <v>11250</v>
+      </c>
+      <c r="G23" s="5">
+        <v>17500</v>
+      </c>
+      <c r="H23" s="5">
+        <v>28500</v>
+      </c>
+      <c r="I23" s="5">
+        <v>33500</v>
+      </c>
+      <c r="J23" s="5">
+        <v>38000</v>
+      </c>
+      <c r="K23" s="5">
+        <v>40000</v>
+      </c>
+      <c r="L23" s="5">
+        <v>46000</v>
+      </c>
+      <c r="M23" s="5">
+        <v>57000</v>
+      </c>
+      <c r="N23" s="5">
+        <v>71000</v>
+      </c>
+      <c r="O23" s="5">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46171</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2322.3000000000002</v>
+      </c>
+      <c r="F24" s="5">
+        <v>11250</v>
+      </c>
+      <c r="G24" s="5">
+        <v>17750</v>
+      </c>
+      <c r="H24" s="5">
+        <v>28500</v>
+      </c>
+      <c r="I24" s="5">
+        <v>33500</v>
+      </c>
+      <c r="J24" s="5">
+        <v>38000</v>
+      </c>
+      <c r="K24" s="5">
+        <v>40000</v>
+      </c>
+      <c r="L24" s="5">
+        <v>46000</v>
+      </c>
+      <c r="M24" s="5">
+        <v>57000</v>
+      </c>
+      <c r="N24" s="5">
+        <v>71000</v>
+      </c>
+      <c r="O24" s="5">
         <v>78000</v>
       </c>
     </row>
@@ -1354,6 +2501,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02768588-2FF0-42C1-8A18-87D4CAFE9D17}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A6084AF-43C5-4F58-881A-79CFC1D1F25A}">
   <dimension ref="B2:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1365,7 +2522,7 @@
       <c r="B2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="11" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1378,6 +2535,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{E64194F6-CA90-47F6-BEDA-E2FFE313AE3F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>